--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>121151067</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151068</v>
+        <v>121151069</v>
       </c>
       <c r="B4" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429946</v>
+        <v>430064</v>
       </c>
       <c r="R4" t="n">
-        <v>6814891</v>
+        <v>6814962</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151069</v>
+        <v>121151068</v>
       </c>
       <c r="B5" t="n">
-        <v>78335</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430064</v>
+        <v>429946</v>
       </c>
       <c r="R5" t="n">
-        <v>6814962</v>
+        <v>6814891</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151067</v>
+        <v>121151068</v>
       </c>
       <c r="B3" t="n">
-        <v>79190</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429849</v>
+        <v>429946</v>
       </c>
       <c r="R3" t="n">
-        <v>6814777</v>
+        <v>6814891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151069</v>
+        <v>121151067</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>79190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430064</v>
+        <v>429849</v>
       </c>
       <c r="R4" t="n">
-        <v>6814962</v>
+        <v>6814777</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151068</v>
+        <v>121151069</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>78338</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429946</v>
+        <v>430064</v>
       </c>
       <c r="R5" t="n">
-        <v>6814891</v>
+        <v>6814962</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>121151068</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151067</v>
+        <v>121151069</v>
       </c>
       <c r="B4" t="n">
-        <v>79190</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429849</v>
+        <v>430064</v>
       </c>
       <c r="R4" t="n">
-        <v>6814777</v>
+        <v>6814962</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151069</v>
+        <v>121151067</v>
       </c>
       <c r="B5" t="n">
-        <v>78338</v>
+        <v>79193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430064</v>
+        <v>429849</v>
       </c>
       <c r="R5" t="n">
-        <v>6814962</v>
+        <v>6814777</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151068</v>
+        <v>121151067</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>79193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429946</v>
+        <v>429849</v>
       </c>
       <c r="R3" t="n">
-        <v>6814891</v>
+        <v>6814777</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151067</v>
+        <v>121151068</v>
       </c>
       <c r="B5" t="n">
-        <v>79193</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429849</v>
+        <v>429946</v>
       </c>
       <c r="R5" t="n">
-        <v>6814777</v>
+        <v>6814891</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58508-2021 artfynd.xlsx
+++ b/artfynd/A 58508-2021 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151067</v>
+        <v>121151069</v>
       </c>
       <c r="B3" t="n">
-        <v>79193</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429849</v>
+        <v>430064</v>
       </c>
       <c r="R3" t="n">
-        <v>6814777</v>
+        <v>6814962</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151069</v>
+        <v>121151067</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430064</v>
+        <v>429849</v>
       </c>
       <c r="R4" t="n">
-        <v>6814962</v>
+        <v>6814777</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,7 +1022,7 @@
         <v>121151068</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
